--- a/Data/tables/sub_attribute_info.xlsx
+++ b/Data/tables/sub_attribute_info.xlsx
@@ -431,19 +431,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SubProcessID</t>
+          <t>stream:datastream</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>dict</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>time:timestamp</t>
+          <t>operation_end_time</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -455,31 +455,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>stream:datastream</t>
+          <t>concept:name</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dict</t>
+          <t>str</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>operation_end_time</t>
+          <t>org:resource</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>str</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>org:resource</t>
+          <t>SubProcessID</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -491,12 +491,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>concept:name</t>
+          <t>time:timestamp</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>datetime</t>
         </is>
       </c>
     </row>

--- a/Data/tables/sub_attribute_info.xlsx
+++ b/Data/tables/sub_attribute_info.xlsx
@@ -431,24 +431,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>stream:datastream</t>
+          <t>SubProcessID</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dict</t>
+          <t>str</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>operation_end_time</t>
+          <t>stream:datastream</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>dict</t>
         </is>
       </c>
     </row>
@@ -467,19 +467,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>org:resource</t>
+          <t>time:timestamp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>datetime</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SubProcessID</t>
+          <t>org:resource</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -491,7 +491,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time:timestamp</t>
+          <t>operation_end_time</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">

--- a/Data/tables/sub_attribute_info.xlsx
+++ b/Data/tables/sub_attribute_info.xlsx
@@ -443,55 +443,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stream:datastream</t>
+          <t>org:resource</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dict</t>
+          <t>str</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>concept:name</t>
+          <t>operation_end_time</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>datetime</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>time:timestamp</t>
+          <t>concept:name</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>str</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>org:resource</t>
+          <t>stream:datastream</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>dict</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>operation_end_time</t>
+          <t>time:timestamp</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">

--- a/Data/tables/sub_attribute_info.xlsx
+++ b/Data/tables/sub_attribute_info.xlsx
@@ -431,43 +431,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SubProcessID</t>
+          <t>time:timestamp</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>datetime</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>org:resource</t>
+          <t>stream:datastream</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>dict</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>operation_end_time</t>
+          <t>org:resource</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>str</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>concept:name</t>
+          <t>SubProcessID</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -479,19 +479,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>stream:datastream</t>
+          <t>concept:name</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dict</t>
+          <t>str</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time:timestamp</t>
+          <t>operation_end_time</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">

--- a/Data/tables/sub_attribute_info.xlsx
+++ b/Data/tables/sub_attribute_info.xlsx
@@ -443,19 +443,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stream:datastream</t>
+          <t>operation_end_time</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dict</t>
+          <t>datetime</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>org:resource</t>
+          <t>concept:name</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -467,19 +467,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SubProcessID</t>
+          <t>stream:datastream</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>str</t>
+          <t>dict</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>concept:name</t>
+          <t>SubProcessID</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -491,12 +491,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>operation_end_time</t>
+          <t>org:resource</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>str</t>
         </is>
       </c>
     </row>
